--- a/Examples/AcPowerSystem/PNSequenceControl_SingleBus＆4Bus/InfBus_GflPN.xlsx
+++ b/Examples/AcPowerSystem/PNSequenceControl_SingleBus＆4Bus/InfBus_GflPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Simplus-Grid-Tool-master-latest_version\Examples\阳光电源\单机系统\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Simplus-Grid-Tool-master-latest_version\Examples\AcPowerSystem\PNSequenceControl_SingleBus＆4Bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6421F049-D84E-47AD-9342-C4A4D65B18DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26351AC-A0DA-42D0-9F1E-BA9B2A13E1F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10392" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,9 +93,6 @@
     <t>Rc</t>
   </si>
   <si>
-    <t>f_power</t>
-  </si>
-  <si>
     <t>kp</t>
   </si>
   <si>
@@ -220,6 +217,10 @@
   </si>
   <si>
     <t>Enable_Participation</t>
+  </si>
+  <si>
+    <t>f_pll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -781,42 +782,42 @@
         <v>21</v>
       </c>
       <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>28</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>29</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -898,7 +899,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -908,12 +909,12 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -928,25 +929,25 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -979,7 +980,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -989,25 +990,25 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
       <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>46</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>47</v>
-      </c>
-      <c r="G3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1056,7 +1057,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1066,7 +1067,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="7">
         <f>12.5*1000</f>
@@ -1075,7 +1076,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="8">
         <v>50</v>
@@ -1083,7 +1084,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1091,7 +1092,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1115,7 +1116,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1125,7 +1126,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1133,7 +1134,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1141,7 +1142,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1149,7 +1150,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1157,7 +1158,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1165,7 +1166,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1173,7 +1174,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1181,7 +1182,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1189,7 +1190,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1197,7 +1198,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12">
         <v>0</v>
